--- a/DateBase/orders/Nha Thu_2026-3-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -772,10 +772,40 @@
       <c r="A41" t="str">
         <v>7</v>
       </c>
+      <c r="C41" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F41" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L44"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -830,7 +860,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010415125205810751031010151055555101551210100205201010552010100</v>
+        <v>010104151252058107510310101510555551015512101002052010105520101015151520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-17.xlsx
@@ -862,6 +862,9 @@
       <c r="G2" t="str">
         <v>010104151252058107510310101510555551015512101002052010105520101015151520</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
